--- a/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
+++ b/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
@@ -436,19 +436,6 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -700,7 +687,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -724,8 +711,10 @@
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I6" s="3" t="n">
         <v>60</v>
@@ -801,27 +790,25 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Tegang dan penuh kekhawatiran warga kampung</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Riuh, bangga, dan penuh decak kagum warga atas keberhasilan Rian</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Sunyi senyap karena hujan badai yang sangat lebat</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Kecewa karena perahu robot tersangkut ranting pohon</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
-        <v>2</v>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I8" s="3" t="n">
         <v>60</v>
@@ -1026,7 +1013,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1050,8 +1037,10 @@
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I13" s="3" t="n">
         <v>60</v>
@@ -1178,27 +1167,25 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Makanan pokok dan sayur-mayur</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Lauk-pauk dan buah-buahan</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Makanan pokok dan lauk-pauk</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Sayur-mayur dan buah-buahan</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="n">
-        <v>1</v>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I16" s="3" t="n">
         <v>60</v>
@@ -1312,7 +1299,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Multiple Choice</t>
+          <t>Checkbox</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1336,8 +1323,10 @@
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>1</v>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>1, 3</t>
+        </is>
       </c>
       <c r="I19" s="3" t="n">
         <v>60</v>
@@ -1409,27 +1398,25 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Rombongan wisatawan itu berlayar menyeberangi Selat Bali pada hari Minggu.</t>
+          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Danau toba merupakan Danau vulkanik terbesar di Asia Tenggara.</t>
+          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Ibu membeli buah Pisang ambon di pasar Tradisional.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Setiap hari selasa, siswa kelas Enam memakai seragam pramuka.</t>
-        </is>
-      </c>
+          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I21" s="3" t="n">
         <v>60</v>

--- a/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
+++ b/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
@@ -682,7 +682,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan berikut yang merupakan FAKTA yang dapat diverifikasi dari teks 'PLTS Terapung Cirata' adalah....</t>
+          <t>Berdasarkan teks 'PLTS Terapung Cirata', manakah pernyataan yang merupakan FAKTA? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -692,22 +692,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PLTS Terapung Cirata dibangun di atas permukaan waduk dengan kapasitas daya mencapai 192 MWp.</t>
+          <t>PLTS Terapung Cirata dibangun di atas Waduk Cirata dengan kapasitas 192 MWp.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Semua pembangkit listrik tenaga batu bara di Indonesia sebaiknya ditutup tahun depan.</t>
+          <t>Semua PLTU batu bara di Indonesia harus ditutup segera.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Energi matahari adalah satu-satunya sumber energi yang disukai masyarakat Jawa Barat.</t>
+          <t>Energi surya adalah energi terbarukan yang ramah lingkungan.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Pemandangan panel surya di Waduk Cirata terlihat paling indah di seluruh dunia.</t>
+          <t>PLTS Cirata adalah yang paling indah di dunia.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
@@ -722,7 +722,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Pilihan A menyajikan data faktual angka terukur: berkapasitas 192 MWp di Waduk Cirata. Pilihan B, C, dan D merupakan opini, saran subjektif, atau klaim berlebihan. Jawaban yang tepat adalah A.</t>
+          <t>A: Fakta (angka terukur 192 MWp, lokasi Waduk Cirata). B: Opini (harus ditutup = pendapat). C: Fakta (energi surya terbarukan &amp; ramah lingkungan). D: Opini (paling indah = subjektif). Jawaban benar: A, C.</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Suasana yang tercipta pada bagian akhir cerita saat robot buatan Rian berhasil bekerja adalah....</t>
+          <t>Berdasarkan cerita robot Rian, tentukan kebenaran pernyataan berikut!</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -790,17 +790,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Suasana awal cerita cemas karena hujan badai.</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Suasana akhir cerita riah, bangga, dan penuh decak kagum warga.</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Robot Rian gagal berfungsi dan membuat warga kecewa.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
@@ -816,7 +816,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Di akhir cerita digambarkan: 'Warga kampung yang berkumpul di pinggir jalan bertepuk tangan riuh, kagum atas keuletan dan kecerdasan anak muda yang peduli pada lingkungannya tersebut.' Suasana yang tercipta adalah bangga dan kagum (Pilihan B).</t>
+          <t>A: SALAH (awal cerita Rian membuat robot, bukan hujan badai). B: BENAR (teks: 'warga bertepuk tangan riuh, bangga, decak kagum'). C: SALAH (robot BERHASIL bekerja).</t>
         </is>
       </c>
     </row>
@@ -1008,7 +1008,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Berdasarkan teks di atas, salah satu tujuan mulia dari penggunaan kain penutup saat tawar-menawar Marosok adalah....</t>
+          <t>Berdasarkan teks tradisi Marosok, tujuan penggunaan kain penutup saat tawar-menawar adalah.... (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1018,28 +1018,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Menghangatkan tangan pembeli dan penjual dari cuaca dingin pegunungan</t>
+          <t>Menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat dan menghindarkan rasa malu pembeli</t>
+          <t>Menghindarkan rasa malu pembeli jika harganya tidak terjangkau.</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan status sosial dan kekayaan keluarga pembeli ternak</t>
+          <t>Menghangatkan tangan saat berunding di cuaca dingin.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Menghitung jumlah uang kertas yang dibawa oleh calon pembeli</t>
+          <t>Menunjukkan kekayaan pembeli melalui kain yang dipakai.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2</t>
         </is>
       </c>
       <c r="I13" s="3" t="n">
@@ -1048,7 +1048,7 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Paragraf ketiga memaparkan filosofinya: menjaga privasi harga agar pembeli lain tidak tahu sehingga persaingan tidak sehat dapat dicegah, serta menjaga martabat/menghindarkan rasa malu pembeli jika tawarannya belum cocok (Pilihan B).</t>
+          <t>A &amp; B: Benar (teks: 'menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat dan menghindarkan rasa malu pembeli'). C: SALAH (bukan tujuan utama). D: SALAH (bukan untuk menunjukkan kekayaan). Jawaban benar: A, B.</t>
         </is>
       </c>
     </row>
@@ -1145,19 +1145,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Bacalah poster edukasi kesehatan berikut untuk menjawab soal nomor 15 dan 16!
-Panduan Gizi Seimbang Generasi Hebat: Gerakan 'Isi Piringku'
-Kementerian Kesehatan RI mengajak keluarga Indonesia menerapkan pedoman gizi seimbang sekali makan:
-- 2/3 dari setengah piring diisi MAKANAN POKOK (nasi, jagung, singkong, ubi) sebagai sumber energi utama.
-- 1/3 dari setengah piring diisi LAUK-PAUK (ikan, ayam, telur, tempe, tahu) kaya protein dan mineral.
-- 2/3 dari setengah piring lainnya diisi SAYUR-MAYUR segar aneka warna sumber serat dan vitamin.
-- 1/3 dari setengah piring lainnya diisi BUAH-BUAHAN lokal manis kaya antioksidan.
-Lengkapi piring sehatmu dengan 4 Pilar Gaya Hidup Sehat:
-(1) Cuci tangan pakai sabun dengan air mengalir sebelum dan sesudah makan.
-(2) Minum air putih minimal 8 gelas per hari untuk menjaga hidrasi tubuh.
-(3) Lakukan aktivitas fisik atau olahraga ringan minimal 30 menit setiap hari.
-(4) Pantau berat badan secara rutin setiap bulan.
-Berdasarkan panduan 'Isi Piringku' dalam poster edukasi di atas, kelompok makanan yang memiliki porsi seimbang sebesar 2/3 dari setengah piring adalah....</t>
+          <t>Berdasarkan poster 'Gizi Seimbang Generasi Hebat', tentukan kebenaran!</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1167,17 +1155,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Makanan pokok mengisi 2/3 dari setengah piring.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Sayur-mayur mengisi 1/3 dari setengah piring.</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Lauk-pauk dan buah-buahan masing-masing mengisi 1/4 piring penuh.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr"/>
@@ -1193,7 +1181,7 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Dalam poster tertulis: Makanan pokok mengambil 2/3 dari setengah piring, dan sayur-mayur juga mengambil 2/3 dari setengah piring lainnya. Keduanya berimbang besar (Pilihan A).</t>
+          <t>A: BENAR (poster: nasi 2/3 dari ½ piring). B: BENAR (sayur 1/3 dari ½ piring). C: SALAH (lauk 1/3 dari ½ piring, buah 1/3 dari ½ piring, BUKAN 1/4 piring penuh).</t>
         </is>
       </c>
     </row>
@@ -1292,9 +1280,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Perhatikan kalimat berikut!
-Pemerintah kota terus berupaya (luas) jalur hijau di sepanjang trotoar demi menyerap emisi kendaraan bermotor.
-Bentuk kata berimbuhan yang tepat untuk kata dalam tanda kurung agar membentuk kalimat yang efektif adalah....</t>
+          <t>Perhatikan pasangan kata berikut! (1) luas → memperluas, (2) panjang → memanjangkan, (3) dalam → memperdalam, (4) tinggi → memertinggikan. Manakah pasangan yang TEPAT? (Pilih lebih dari satu)</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1304,28 +1290,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>memperluas</t>
+          <t>luas → memperluas (tepat).</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>meluaskan</t>
+          <t>panjang → memanjangkan (tepat).</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>diperluas</t>
+          <t>dalam → memperdalam (tepat).</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>memperluaskan</t>
+          <t>tinggi → memertinggikan (tepat).</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t>1, 3</t>
+          <t>1, 2, 3, 4</t>
         </is>
       </c>
       <c r="I19" s="3" t="n">
@@ -1334,7 +1320,7 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Kata dasar 'luas' merupakan kata sifat. Imbuhan pembentuk kata kerja yang menyatakan 'menjadikan lebih luas' adalah 'memper-' (memperluas). Bentuk 'memperluaskan' salah karena pleonasme (tumpang tindih afiks memper-...-kan pada kata sifat). Jadi kata yang baku dan tepat adalah 'memperluas' (Pilihan A).</t>
+          <t>Semua pasangan tepat: luas-memperluas, panjang-memanjangkan, dalam-memperdalam, tinggi-memertinggikan (imbuhan memper- + kan pada kata sifat). Jawaban benar: A, B, C, D.</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1374,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Penulisan huruf kapital berikut yang tepat dan sesuai dengan kaidah EYD adalah....</t>
+          <t>Tentukan kebenaran penulisan huruf kapital berikut!</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1398,17 +1384,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan pertama berkaitan dengan konsep dasar materi ini.</t>
+          <t>Selat Bali, hari Minggu → Penulisan BENAR.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Hasil perhitungan akhir bernilai lebih dari 50.</t>
+          <t>Danau Toba, Gunung Merapi → Penulisan BENAR.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Pernyataan ketiga bernilai salah berdasarkan analisis rumus.</t>
+          <t>Pisang Ambon, Pasar Tradisional → Penulisan BENAR.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr"/>
@@ -1424,12 +1410,7 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Analisis ejaan:
-- Pilihan A: BENAR. Nama diri geografi (Selat Bali) huruf kapital, nama hari (Minggu) huruf kapital.
-- Pilihan B: salah, harusnya Danau Toba (T kapital), 'danau' pada danau vulkanik huruf kecil.
-- Pilihan C: salah, pisang ambon adalah nama jenis (bukan nama diri), jadi p dan a huruf kecil.
-- Pilihan D: salah, selasa harus kapital (Selasa), enam huruf kecil.
-Jadi kalimat yang benar adalah A.</t>
+          <t>A: BENAR (Selat Bali = nama geografi, Minggu = hari). B: BENAR (Danau Toba, Gunung Merapi = nama geografi). C: SALAH (pisang ambon = jenis buah, bukan nama diri → huruf kecil; pasar tradisional = umum, bukan nama diri).</t>
         </is>
       </c>
     </row>

--- a/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
+++ b/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
@@ -436,6 +436,19 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="45" customWidth="1" min="11" max="11"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -682,39 +695,37 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Berdasarkan teks 'PLTS Terapung Cirata', manakah pernyataan yang merupakan FAKTA? (Pilih lebih dari satu)</t>
+          <t>Pernyataan berikut yang merupakan FAKTA yang dapat diverifikasi dari teks 'PLTS Terapung Cirata' adalah....</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>PLTS Terapung Cirata dibangun di atas Waduk Cirata dengan kapasitas 192 MWp.</t>
+          <t>PLTS Terapung Cirata dibangun di atas permukaan waduk dengan kapasitas daya mencapai 192 MWp.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Semua PLTU batu bara di Indonesia harus ditutup segera.</t>
+          <t>Semua pembangkit listrik tenaga batu bara di Indonesia sebaiknya ditutup tahun depan.</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Energi surya adalah energi terbarukan yang ramah lingkungan.</t>
+          <t>Energi matahari adalah satu-satunya sumber energi yang disukai masyarakat Jawa Barat.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>PLTS Cirata adalah yang paling indah di dunia.</t>
+          <t>Pemandangan panel surya di Waduk Cirata terlihat paling indah di seluruh dunia.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>1, 3</t>
-        </is>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>60</v>
@@ -722,7 +733,7 @@
       <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>A: Fakta (angka terukur 192 MWp, lokasi Waduk Cirata). B: Opini (harus ditutup = pendapat). C: Fakta (energi surya terbarukan &amp; ramah lingkungan). D: Opini (paling indah = subjektif). Jawaban benar: A, C.</t>
+          <t>Pilihan A menyajikan data faktual angka terukur: berkapasitas 192 MWp di Waduk Cirata. Pilihan B, C, dan D merupakan opini, saran subjektif, atau klaim berlebihan. Jawaban yang tepat adalah A.</t>
         </is>
       </c>
     </row>
@@ -780,7 +791,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Berdasarkan cerita robot Rian, tentukan kebenaran pernyataan berikut!</t>
+          <t>Suasana yang tercipta pada bagian akhir cerita saat robot buatan Rian berhasil bekerja adalah....</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -790,25 +801,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Suasana awal cerita cemas karena hujan badai.</t>
+          <t>Tegang dan penuh kekhawatiran warga kampung</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Suasana akhir cerita riah, bangga, dan penuh decak kagum warga.</t>
+          <t>Riuh, bangga, dan penuh decak kagum warga atas keberhasilan Rian</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Robot Rian gagal berfungsi dan membuat warga kecewa.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
+          <t>Sunyi senyap karena hujan badai yang sangat lebat</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Kecewa karena perahu robot tersangkut ranting pohon</t>
+        </is>
+      </c>
       <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H8" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>60</v>
@@ -816,7 +829,7 @@
       <c r="J8" s="3" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>A: SALAH (awal cerita Rian membuat robot, bukan hujan badai). B: BENAR (teks: 'warga bertepuk tangan riuh, bangga, decak kagum'). C: SALAH (robot BERHASIL bekerja).</t>
+          <t>Di akhir cerita digambarkan: 'Warga kampung yang berkumpul di pinggir jalan bertepuk tangan riuh, kagum atas keuletan dan kecerdasan anak muda yang peduli pada lingkungannya tersebut.' Suasana yang tercipta adalah bangga dan kagum (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -1008,39 +1021,37 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Berdasarkan teks tradisi Marosok, tujuan penggunaan kain penutup saat tawar-menawar adalah.... (Pilih lebih dari satu)</t>
+          <t>Berdasarkan teks di atas, salah satu tujuan mulia dari penggunaan kain penutup saat tawar-menawar Marosok adalah....</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat.</t>
+          <t>Menghangatkan tangan pembeli dan penjual dari cuaca dingin pegunungan</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Menghindarkan rasa malu pembeli jika harganya tidak terjangkau.</t>
+          <t>Menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat dan menghindarkan rasa malu pembeli</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Menghangatkan tangan saat berunding di cuaca dingin.</t>
+          <t>Menunjukkan status sosial dan kekayaan keluarga pembeli ternak</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan kekayaan pembeli melalui kain yang dipakai.</t>
+          <t>Menghitung jumlah uang kertas yang dibawa oleh calon pembeli</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>1, 2</t>
-        </is>
+      <c r="H13" s="3" t="n">
+        <v>2</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>60</v>
@@ -1048,7 +1059,7 @@
       <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>A &amp; B: Benar (teks: 'menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat dan menghindarkan rasa malu pembeli'). C: SALAH (bukan tujuan utama). D: SALAH (bukan untuk menunjukkan kekayaan). Jawaban benar: A, B.</t>
+          <t>Paragraf ketiga memaparkan filosofinya: menjaga privasi harga agar pembeli lain tidak tahu sehingga persaingan tidak sehat dapat dicegah, serta menjaga martabat/menghindarkan rasa malu pembeli jika tawarannya belum cocok (Pilihan B).</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1156,19 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Berdasarkan poster 'Gizi Seimbang Generasi Hebat', tentukan kebenaran!</t>
+          <t>Bacalah poster edukasi kesehatan berikut untuk menjawab soal nomor 15 dan 16!
+Panduan Gizi Seimbang Generasi Hebat: Gerakan 'Isi Piringku'
+Kementerian Kesehatan RI mengajak keluarga Indonesia menerapkan pedoman gizi seimbang sekali makan:
+- 2/3 dari setengah piring diisi MAKANAN POKOK (nasi, jagung, singkong, ubi) sebagai sumber energi utama.
+- 1/3 dari setengah piring diisi LAUK-PAUK (ikan, ayam, telur, tempe, tahu) kaya protein dan mineral.
+- 2/3 dari setengah piring lainnya diisi SAYUR-MAYUR segar aneka warna sumber serat dan vitamin.
+- 1/3 dari setengah piring lainnya diisi BUAH-BUAHAN lokal manis kaya antioksidan.
+Lengkapi piring sehatmu dengan 4 Pilar Gaya Hidup Sehat:
+(1) Cuci tangan pakai sabun dengan air mengalir sebelum dan sesudah makan.
+(2) Minum air putih minimal 8 gelas per hari untuk menjaga hidrasi tubuh.
+(3) Lakukan aktivitas fisik atau olahraga ringan minimal 30 menit setiap hari.
+(4) Pantau berat badan secara rutin setiap bulan.
+Berdasarkan panduan 'Isi Piringku' dalam poster edukasi di atas, kelompok makanan yang memiliki porsi seimbang sebesar 2/3 dari setengah piring adalah....</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1155,25 +1178,27 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Makanan pokok mengisi 2/3 dari setengah piring.</t>
+          <t>Makanan pokok dan sayur-mayur</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sayur-mayur mengisi 1/3 dari setengah piring.</t>
+          <t>Lauk-pauk dan buah-buahan</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Lauk-pauk dan buah-buahan masing-masing mengisi 1/4 piring penuh.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr"/>
+          <t>Makanan pokok dan lauk-pauk</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Sayur-mayur dan buah-buahan</t>
+        </is>
+      </c>
       <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H16" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>60</v>
@@ -1181,7 +1206,7 @@
       <c r="J16" s="3" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>A: BENAR (poster: nasi 2/3 dari ½ piring). B: BENAR (sayur 1/3 dari ½ piring). C: SALAH (lauk 1/3 dari ½ piring, buah 1/3 dari ½ piring, BUKAN 1/4 piring penuh).</t>
+          <t>Dalam poster tertulis: Makanan pokok mengambil 2/3 dari setengah piring, dan sayur-mayur juga mengambil 2/3 dari setengah piring lainnya. Keduanya berimbang besar (Pilihan A).</t>
         </is>
       </c>
     </row>
@@ -1280,39 +1305,39 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Perhatikan pasangan kata berikut! (1) luas → memperluas, (2) panjang → memanjangkan, (3) dalam → memperdalam, (4) tinggi → memertinggikan. Manakah pasangan yang TEPAT? (Pilih lebih dari satu)</t>
+          <t>Perhatikan kalimat berikut!
+Pemerintah kota terus berupaya (luas) jalur hijau di sepanjang trotoar demi menyerap emisi kendaraan bermotor.
+Bentuk kata berimbuhan yang tepat untuk kata dalam tanda kurung agar membentuk kalimat yang efektif adalah....</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Checkbox</t>
+          <t>Multiple Choice</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>luas → memperluas (tepat).</t>
+          <t>memperluas</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>panjang → memanjangkan (tepat).</t>
+          <t>meluaskan</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>dalam → memperdalam (tepat).</t>
+          <t>diperluas</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>tinggi → memertinggikan (tepat).</t>
+          <t>memperluaskan</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="inlineStr">
-        <is>
-          <t>1, 2, 3, 4</t>
-        </is>
+      <c r="H19" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I19" s="3" t="n">
         <v>60</v>
@@ -1320,7 +1345,7 @@
       <c r="J19" s="3" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Semua pasangan tepat: luas-memperluas, panjang-memanjangkan, dalam-memperdalam, tinggi-memertinggikan (imbuhan memper- + kan pada kata sifat). Jawaban benar: A, B, C, D.</t>
+          <t>Kata dasar 'luas' merupakan kata sifat. Imbuhan pembentuk kata kerja yang menyatakan 'menjadikan lebih luas' adalah 'memper-' (memperluas). Bentuk 'memperluaskan' salah karena pleonasme (tumpang tindih afiks memper-...-kan pada kata sifat). Jadi kata yang baku dan tepat adalah 'memperluas' (Pilihan A).</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1399,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Tentukan kebenaran penulisan huruf kapital berikut!</t>
+          <t>Penulisan huruf kapital berikut yang tepat dan sesuai dengan kaidah EYD adalah....</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1384,25 +1409,27 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Selat Bali, hari Minggu → Penulisan BENAR.</t>
+          <t>Rombongan wisatawan itu berlayar menyeberangi Selat Bali pada hari Minggu.</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Danau Toba, Gunung Merapi → Penulisan BENAR.</t>
+          <t>Danau toba merupakan Danau vulkanik terbesar di Asia Tenggara.</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Pisang Ambon, Pasar Tradisional → Penulisan BENAR.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>Ibu membeli buah Pisang ambon di pasar Tradisional.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Setiap hari selasa, siswa kelas Enam memakai seragam pramuka.</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="H21" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>60</v>
@@ -1410,7 +1437,12 @@
       <c r="J21" s="3" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>A: BENAR (Selat Bali = nama geografi, Minggu = hari). B: BENAR (Danau Toba, Gunung Merapi = nama geografi). C: SALAH (pisang ambon = jenis buah, bukan nama diri → huruf kecil; pasar tradisional = umum, bukan nama diri).</t>
+          <t>Analisis ejaan:
+- Pilihan A: BENAR. Nama diri geografi (Selat Bali) huruf kapital, nama hari (Minggu) huruf kapital.
+- Pilihan B: salah, harusnya Danau Toba (T kapital), 'danau' pada danau vulkanik huruf kecil.
+- Pilihan C: salah, pisang ambon adalah nama jenis (bukan nama diri), jadi p dan a huruf kecil.
+- Pilihan D: salah, selasa harus kapital (Selasa), enam huruf kecil.
+Jadi kalimat yang benar adalah A.</t>
         </is>
       </c>
     </row>

--- a/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
+++ b/Quiz_Web_Bahasa_Indonesia_Paket_2.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,25 +25,13 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="004F46E5"/>
-        <bgColor rgb="004F46E5"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -58,17 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -436,79 +415,66 @@
   </sheetPr>
   <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
-    <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="45" customWidth="1" min="11" max="11"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Question Text</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Question Type</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Option 1</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Option 2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Option 3</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Option 4</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Option 5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Correct Answer</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Time in seconds</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Image Link</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Explanation</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Bacalah teks informasi berikut dengan cermat untuk menjawab soal nomor 1 sampai 5!
 PLTS Terapung Cirata: Pelopor Energi Hijau Indonesia
@@ -518,227 +484,213 @@
 Gagasan utama yang terdapat pada paragraf pertama teks di atas adalah....</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Proses pemasangan modul panel surya fotovoltaik di Jawa Barat</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Keberhasilan PLTS Terapung Cirata sebagai pelopor pembangkit listrik tenaga surya skala besar di Indonesia</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Penyaluran aliran listrik PLN ke seluruh rumah tangga di pulau Jawa</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Rencana pembangunan waduk buatan di Kabupaten Purwakarta</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="3" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="I2" t="n">
+        <v>60</v>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>Paragraf pertama memaparkan keberadaan PLTS Terapung Cirata sebagai tonggak baru transisi energi hijau di Indonesia, dengan kapasitas 192 MWp dan menjadi terbesar di Asia Tenggara. Gagasan utamanya adalah pilihan B.</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Berdasarkan paragraf kedua, salah satu keunggulan teknis pembangunan panel surya di atas permukaan waduk adalah....</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Memerlukan biaya pemeliharaan mesin yang lebih mahal daripada panel darat</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Suhu air memberikan efek pendinginan alami yang meningkatkan efisiensi penyerapan sinar matahari</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Mampu mengubah air waduk yang kotor menjadi air mineral layak minum</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mempercepat perkembangbiakan tanaman gulma eceng gondok di waduk</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>60</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Pada paragraf kedua dinyatakan: 'Kedua, suhu permukaan air di bawah panel surya memberikan efek pendinginan alami (cooling effect) yang menjaga kestabilan temperatur modul, sehingga efisiensi penyerapan sinar matahari meningkat...' Jadi jawabannya adalah B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Makna istilah 'energi terbarukan' pada paragraf ketiga teks bacaan tersebut adalah....</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>60</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Energi terbarukan (renewable energy) adalah sumber energi yang dapat diperbarui secara alami dan berkelanjutan (seperti matahari, angin, air, dan panas bumi) serta ramah lingkungan. Pilihan yang tepat adalah B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Mengapa keberadaan deretan panel surya terapung dapat bermanfaat bagi kelestarian air waduk saat musim kemarau?</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Memerlukan biaya pemeliharaan mesin yang lebih mahal daripada panel darat</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Suhu air memberikan efek pendinginan alami yang meningkatkan efisiensi penyerapan sinar matahari</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Mampu mengubah air waduk yang kotor menjadi air mineral layak minum</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Mempercepat perkembangbiakan tanaman gulma eceng gondok di waduk</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="3" t="n">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Karena panel surya menyedot air waduk untuk pendingin baterai</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Karena naungan panel surya mengurangi laju penguapan air (evaporasi) waduk</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Karena panel surya mendatangkan awan hujan buatan di atas perairan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Karena air waduk dialirkan keluar menuju saluran irigasi sawah</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Pada paragraf kedua dinyatakan: 'Kedua, suhu permukaan air di bawah panel surya memberikan efek pendinginan alami (cooling effect) yang menjaga kestabilan temperatur modul, sehingga efisiensi penyerapan sinar matahari meningkat...' Jadi jawabannya adalah B.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Makna istilah 'energi terbarukan' pada paragraf ketiga teks bacaan tersebut adalah....</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Sumber energi yang berasal dari pembakaran bahan tambang minyak bumi</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Sumber energi yang berasal dari proses alam berkelanjutan dan tidak akan pernah habis</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Energi yang hanya dapat dipergunakan satu kali kemudian musnah</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Bahan bakar fosil yang diproduksi oleh pabrik pengolahan batu bara</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I4" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Energi terbarukan (renewable energy) adalah sumber energi yang dapat diperbarui secara alami dan berkelanjutan (seperti matahari, angin, air, dan panas bumi) serta ramah lingkungan. Pilihan yang tepat adalah B.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Mengapa keberadaan deretan panel surya terapung dapat bermanfaat bagi kelestarian air waduk saat musim kemarau?</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Karena panel surya menyedot air waduk untuk pendingin baterai</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Karena naungan panel surya mengurangi laju penguapan air (evaporasi) waduk</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Karena panel surya mendatangkan awan hujan buatan di atas perairan</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Karena air waduk dialirkan keluar menuju saluran irigasi sawah</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I5" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>Pada paragraf kedua tertulis: 'Ketiga, naungan deretan panel surya di atas permukaan waduk mampu mengurangi laju penguapan air (evaporasi) saat musim kemarau...' Pilihan yang benar adalah B.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Pernyataan berikut yang merupakan FAKTA yang dapat diverifikasi dari teks 'PLTS Terapung Cirata' adalah....</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>PLTS Terapung Cirata dibangun di atas permukaan waduk dengan kapasitas daya mencapai 192 MWp.</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Semua pembangkit listrik tenaga batu bara di Indonesia sebaiknya ditutup tahun depan.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Energi matahari adalah satu-satunya sumber energi yang disukai masyarakat Jawa Barat.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Pemandangan panel surya di Waduk Cirata terlihat paling indah di seluruh dunia.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>60</v>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>Pilihan A menyajikan data faktual angka terukur: berkapasitas 192 MWp di Waduk Cirata. Pilihan B, C, dan D merupakan opini, saran subjektif, atau klaim berlebihan. Jawaban yang tepat adalah A.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Bacalah cerita inspiratif berikut dengan cermat untuk menjawab soal nomor 6 sampai 10!
 Robot Perahu Pembersih Parit Karya Rian
@@ -749,227 +701,203 @@
 Sikap pantang menyerah tokoh Rian dalam cerita di atas ditunjukkan ketika....</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>60</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Ketika baling-balingnya patah dan disuruh menyerah oleh teman-temannya, Rian justru menyatakan bahwa kegagalan adalah pelajaran berharga dan ia memperbaiki baling-baling serta menyegel wadah baterai dengan silikon (Pilihan B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Suasana yang tercipta pada bagian akhir cerita saat robot buatan Rian berhasil bekerja adalah....</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Menolak ajakan teman-temannya untuk bermain layang-layang di lapangan</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Tidak putus asa saat robot perahunya rusak pada uji coba pertama dan segera memperbaiki kelemahannya</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Meminta ayahnya membelikan komponen robot perahu yang baru dan mahal dari toko</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Membiarkan sampah di parit menumpuk hingga musim hujan berakhir</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="3" t="n">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tegang dan penuh kekhawatiran warga kampung</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Riuh, bangga, dan penuh decak kagum warga atas keberhasilan Rian</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Sunyi senyap karena hujan badai yang sangat lebat</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kecewa karena perahu robot tersangkut ranting pohon</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Ketika baling-balingnya patah dan disuruh menyerah oleh teman-temannya, Rian justru menyatakan bahwa kegagalan adalah pelajaran berharga dan ia memperbaiki baling-baling serta menyegel wadah baterai dengan silikon (Pilihan B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Suasana yang tercipta pada bagian akhir cerita saat robot buatan Rian berhasil bekerja adalah....</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="I8" t="n">
+        <v>60</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Di akhir cerita digambarkan: 'Warga kampung yang berkumpul di pinggir jalan bertepuk tangan riuh, kagum atas keuletan dan kecerdasan anak muda yang peduli pada lingkungannya tersebut.' Suasana yang tercipta adalah bangga dan kagum (Pilihan B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Penyebab utama rusaknya robot perahu milik Rian pada saat uji coba pertama di parit kampung adalah....</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Baterai mobil mainannya kehabisan daya listrik di tengah jalan</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Baling-baling perahu membentur batu padas dan wadah baterai kemasukan air kotor</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Keranjang jaring tersangkut pada jembatan penyeberangan warga</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rian lupa menyalakan tombol sakelar daya perahu</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>60</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Pada paragraf kedua disebutkan secara jelas: 'Baling-baling perahunya patah menghantam batu padas, dan wadah baterainya kemasukan air kotor hingga mengeluarkan kepulan asap.' Jadi penyebabnya adalah B.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Pesan moral yang ingin disampaikan pengarang melalui kisah perjuangan Rian adalah....</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>60</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Cerita ini menanamkan pesan bahwa kepekaan terhadap lingkungan, dipadukan dengan kreativitas dan ketekunan yang pantang menyerah, akan menghasilkan karya bermanfaat bagi masyarakat (Pilihan B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Peribahasa yang paling tepat untuk menggambarkan tekad dan kegigihan tokoh Rian dalam meraih keberhasilan adalah....</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Tegang dan penuh kekhawatiran warga kampung</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Riuh, bangga, dan penuh decak kagum warga atas keberhasilan Rian</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Sunyi senyap karena hujan badai yang sangat lebat</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Kecewa karena perahu robot tersangkut ranting pohon</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="3" t="n">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Bagai air di daun talas</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Di mana ada kemauan, di situ ada jalan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Besar pasak daripada tiang</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tong kosong nyaring bunyinya</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I8" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Di akhir cerita digambarkan: 'Warga kampung yang berkumpul di pinggir jalan bertepuk tangan riuh, kagum atas keuletan dan kecerdasan anak muda yang peduli pada lingkungannya tersebut.' Suasana yang tercipta adalah bangga dan kagum (Pilihan B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Penyebab utama rusaknya robot perahu milik Rian pada saat uji coba pertama di parit kampung adalah....</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Baterai mobil mainannya kehabisan daya listrik di tengah jalan</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Baling-baling perahu membentur batu padas dan wadah baterai kemasukan air kotor</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Keranjang jaring tersangkut pada jembatan penyeberangan warga</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Rian lupa menyalakan tombol sakelar daya perahu</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Pada paragraf kedua disebutkan secara jelas: 'Baling-baling perahunya patah menghantam batu padas, dan wadah baterainya kemasukan air kotor hingga mengeluarkan kepulan asap.' Jadi penyebabnya adalah B.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>Pesan moral yang ingin disampaikan pengarang melalui kisah perjuangan Rian adalah....</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Masalah kebersihan lingkungan kampung sebaiknya diserahkan kepada petugas kebersihan saja</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Kreativitas dan kegigihan memecahkan masalah akan membuahkan hasil nyata yang bermanfaat bagi sesama</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Membuat barang elektronik dari bahan bekas selalu berisiko gagal dan sia-sia</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Jangan pernah memperlihatkan karya buatan sendiri sebelum benar-benar sempurna</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Cerita ini menanamkan pesan bahwa kepekaan terhadap lingkungan, dipadukan dengan kreativitas dan ketekunan yang pantang menyerah, akan menghasilkan karya bermanfaat bagi masyarakat (Pilihan B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>Peribahasa yang paling tepat untuk menggambarkan tekad dan kegigihan tokoh Rian dalam meraih keberhasilan adalah....</t>
-        </is>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Bagai air di daun talas</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Di mana ada kemauan, di situ ada jalan</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Besar pasak daripada tiang</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Tong kosong nyaring bunyinya</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I11" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="I11" t="n">
+        <v>60</v>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Peribahasa 'Di mana ada kemauan, di situ ada jalan' bermakna jika seseorang bersungguh-sungguh dan memiliki tekad kuat, ia pasti akan menemukan cara untuk mengatasi rintangan dan meraih tujuan (Pilihan B).</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Bacalah teks budaya nusantara berikut untuk menjawab soal nomor 11 sampai 14!
 Tradisi Marosok: Bahasa Isyarat Jari dalam Perdagangan Minangkabau
@@ -979,182 +907,170 @@
 Keunikan utama proses transaksi jual beli dalam tradisi Marosok di Minangkabau adalah....</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Transaksi dilakukan dengan menggunakan pembayaran mata uang emas kuno</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Tawar-menawar harga dilakukan secara hening menggunakan bahasa isyarat jari tangan di balik kain penutup</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Hewan ternak harus dilelang secara terbuka di hadapan tetua adat suku</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pembeli dan penjual wajib menuliskan nominal harga di atas selembar daun lontar</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>60</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Teks menjelaskan secara rinci: transaksi Marosok berlangsung hening tanpa suara lisan, pembeli dan penjual berjabat tangan di bawah kain sarung/penutup dan bernegosiasi menggunakan gerakan dan sentuhan jari-jemari tangan (Pilihan B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Berdasarkan teks di atas, salah satu tujuan mulia dari penggunaan kain penutup saat tawar-menawar Marosok adalah....</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Paragraf ketiga memaparkan filosofinya: menjaga privasi harga agar pembeli lain tidak tahu sehingga persaingan tidak sehat dapat dicegah, serta menjaga martabat/menghindarkan rasa malu pembeli jika tawarannya belum cocok (Pilihan B).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Makna kata 'privasi' dalam kalimat 'menjaga privasi harga antara penjual dan pembeli' adalah....</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Transaksi dilakukan dengan menggunakan pembayaran mata uang emas kuno</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Tawar-menawar harga dilakukan secara hening menggunakan bahasa isyarat jari tangan di balik kain penutup</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Hewan ternak harus dilelang secara terbuka di hadapan tetua adat suku</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Pembeli dan penjual wajib menuliskan nominal harga di atas selembar daun lontar</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="3" t="n">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Kebebasan berbelanja tanpa batasan waktu</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Kerahasiaan atau urusan pribadi yang terlindung dari penglihatan dan pengetahuan orang luar</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Keuntungan finansial yang didapatkan oleh pihak pasar</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kesepakatan tertulis yang disahkan di hadapan notaris hukum</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="I12" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Teks menjelaskan secara rinci: transaksi Marosok berlangsung hening tanpa suara lisan, pembeli dan penjual berjabat tangan di bawah kain sarung/penutup dan bernegosiasi menggunakan gerakan dan sentuhan jari-jemari tangan (Pilihan B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Berdasarkan teks di atas, salah satu tujuan mulia dari penggunaan kain penutup saat tawar-menawar Marosok adalah....</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Menghangatkan tangan pembeli dan penjual dari cuaca dingin pegunungan</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Menjaga kerahasiaan harga agar tidak memicu persaingan tidak sehat dan menghindarkan rasa malu pembeli</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan status sosial dan kekayaan keluarga pembeli ternak</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Menghitung jumlah uang kertas yang dibawa oleh calon pembeli</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>Paragraf ketiga memaparkan filosofinya: menjaga privasi harga agar pembeli lain tidak tahu sehingga persaingan tidak sehat dapat dicegah, serta menjaga martabat/menghindarkan rasa malu pembeli jika tawarannya belum cocok (Pilihan B).</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Makna kata 'privasi' dalam kalimat 'menjaga privasi harga antara penjual dan pembeli' adalah....</t>
-        </is>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Kebebasan berbelanja tanpa batasan waktu</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Kerahasiaan atau urusan pribadi yang terlindung dari penglihatan dan pengetahuan orang luar</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Keuntungan finansial yang didapatkan oleh pihak pasar</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Kesepakatan tertulis yang disahkan di hadapan notaris hukum</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I14" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="I14" t="n">
+        <v>60</v>
+      </c>
+      <c r="K14" t="inlineStr">
         <is>
           <t>Privasi berarti kerahasiaan atau ranah pribadi yang dijaga agar tidak diketahui atau diintervensi oleh orang lain. Pilihan yang tepat adalah B.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Ringkasan yang paling padu dan tepat untuk teks 'Tradisi Marosok' adalah....</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>Pasar ternak di Minangkabau hanya menjual sapi dan kerbau pada hari tertentu dengan pengawasan ketat tetua adat.</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>Tradisi Marosok adalah cara tawar-menawar hewan ternak khas Minangkabau menggunakan isyarat jari di balik kain untuk menjaga etika, privasi harga, dan keharmonisan.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Penggunaan kain sarung dalam perdagangan ternak di Sumatera Barat bertujuan untuk menutupi kekurangan fisik hewan kurban.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>Masyarakat Minangkabau lebih memilih berdagang secara lisan karena dianggap lebih cepat dan praktis.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>60</v>
+      </c>
+      <c r="K15" t="inlineStr">
         <is>
           <t>Ringkasan B merangkum unsur esensial teks: tradisi Marosok, cara kerja isyarat jari di balik penutup, dan nilai filosofis menjaga etika serta privasi harga. Pilihan yang tepat adalah B.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Bacalah poster edukasi kesehatan berikut untuk menjawab soal nomor 15 dan 16!
 Panduan Gizi Seimbang Generasi Hebat: Gerakan 'Isi Piringku'
@@ -1171,271 +1087,247 @@
 Berdasarkan panduan 'Isi Piringku' dalam poster edukasi di atas, kelompok makanan yang memiliki porsi seimbang sebesar 2/3 dari setengah piring adalah....</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>60</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Dalam poster tertulis: Makanan pokok mengambil 2/3 dari setengah piring, dan sayur-mayur juga mengambil 2/3 dari setengah piring lainnya. Keduanya berimbang besar (Pilihan A).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Salah satu pilar pendukung gaya hidup sehat yang dianjurkan dalam pedoman 'Isi Piringku' untuk menjaga metabolisme tubuh adalah....</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Makanan pokok dan sayur-mayur</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Lauk-pauk dan buah-buahan</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Makanan pokok dan lauk-pauk</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Sayur-mayur dan buah-buahan</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Dalam poster tertulis: Makanan pokok mengambil 2/3 dari setengah piring, dan sayur-mayur juga mengambil 2/3 dari setengah piring lainnya. Keduanya berimbang besar (Pilihan A).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>Salah satu pilar pendukung gaya hidup sehat yang dianjurkan dalam pedoman 'Isi Piringku' untuk menjaga metabolisme tubuh adalah....</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Mengurangi waktu istirahat tidur malam</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>Minum air putih minimal 8 gelas per hari dan beraktivitas fisik minimal 30 menit sehari</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Menghindari makan sayuran yang berdaun hijau gelap</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Mengonsumsi suplemen vitamin instan setiap sebelum sarapan</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="3" t="n">
+      <c r="H17" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="I17" t="n">
+        <v>60</v>
+      </c>
+      <c r="K17" t="inlineStr">
         <is>
           <t>Pilar (2) dan (3) menyebutkan: Minum air putih minimal 8 gelas per hari dan aktivitas fisik/olahraga ringan minimal 30 menit sehari (Pilihan B).</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Perhatikan kalimat rumpang berikut!
 Hujan deras mengguyur lapangan upacara sejak pagi hari, [...] para peserta gladi bersih tetap berbaris dengan tertib dan bersemangat.
 Kata penghubung (konjungsi) yang paling tepat untuk melengkapi kalimat majemuk di atas adalah....</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>sehingga</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>karena</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>namun</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>bahkan</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>60</v>
+      </c>
+      <c r="K18" t="inlineStr">
         <is>
           <t>Kalimat tersebut menunjukkan hubungan perlawanan/pertentangan antara situasi hujan lebat dengan semangat peserta upacara yang tidak surut. Konjungsi pertentangan yang tepat adalah 'namun' (atau 'tetapi'). Pilihan yang benar adalah C.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Perhatikan kalimat berikut!
 Pemerintah kota terus berupaya (luas) jalur hijau di sepanjang trotoar demi menyerap emisi kendaraan bermotor.
 Bentuk kata berimbuhan yang tepat untuk kata dalam tanda kurung agar membentuk kalimat yang efektif adalah....</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>memperluas</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>meluaskan</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>diperluas</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>memperluaskan</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr"/>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>True/False</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>60</v>
+      </c>
+      <c r="K19" t="inlineStr">
         <is>
           <t>Kata dasar 'luas' merupakan kata sifat. Imbuhan pembentuk kata kerja yang menyatakan 'menjadikan lebih luas' adalah 'memper-' (memperluas). Bentuk 'memperluaskan' salah karena pleonasme (tumpang tindih afiks memper-...-kan pada kata sifat). Jadi kata yang baku dan tepat adalah 'memperluas' (Pilihan A).</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Perhatikan kalimat berikut!
 Koperasi sekolah menyediakan berbagai macam alat tulis: buku gambar, jangka, busur derajat, dan pensil warna.
 Penggunaan tanda baca titik dua (:) pada kalimat tersebut berfungsi untuk....</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>Multiple Choice</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Mengawali kutipan perkataan langsung tokoh</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" t="inlineStr">
         <is>
           <t>Mengawali suatu pemerincian atau perincian lengkap</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>Memisahkan anak kalimat dari induk kalimat</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>Menutup kalimat yang masih belum selesai disusun</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="3" t="n">
+      <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="I20" t="n">
+        <v>60</v>
+      </c>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Tanda titik dua (:) digunakan pada akhir suatu pernyataan lengkap yang diikuti pemerincian atau penjelasan (buku gambar, jangka, busur derajat, pensil warna). Jadi fungsinya adalah mengawali pemerincian lengkap (Pilihan B).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Penulisan huruf kapital berikut yang tepat dan sesuai dengan kaidah EYD adalah....</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
-        <is>
-          <t>Multiple Choice</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Checkbox</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>Rombongan wisatawan itu berlayar menyeberangi Selat Bali pada hari Minggu.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>Danau toba merupakan Danau vulkanik terbesar di Asia Tenggara.</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Ibu membeli buah Pisang ambon di pasar Tradisional.</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Setiap hari selasa, siswa kelas Enam memakai seragam pramuka.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I21" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Option 1, Option 2</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>60</v>
+      </c>
+      <c r="K21" t="inlineStr">
         <is>
           <t>Analisis ejaan:
 - Pilihan A: BENAR. Nama diri geografi (Selat Bali) huruf kapital, nama hari (Minggu) huruf kapital.
